--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484863_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484863_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6704</v>
+        <v>7.3789</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2676</v>
+        <v>4.9496</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4028</v>
+        <v>2.4293</v>
       </c>
       <c r="G2" t="n">
         <v>5.2183</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7354000000000001</v>
+        <v>1.4439</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0617</v>
+        <v>0.7437</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6737</v>
+        <v>0.7002</v>
       </c>
       <c r="V2" t="n">
         <v>0.9054</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3672</v>
+        <v>5.8602</v>
       </c>
       <c r="E3" t="n">
-        <v>3.303</v>
+        <v>3.8489</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0642</v>
+        <v>2.0113</v>
       </c>
       <c r="G3" t="n">
         <v>2.7607</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2856</v>
+        <v>1.7787</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5349</v>
+        <v>1.0808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7507</v>
+        <v>0.6978</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2813</v>
+        <v>4.5245</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9011</v>
+        <v>2.9856</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3802</v>
+        <v>1.5389</v>
       </c>
       <c r="G4" t="n">
         <v>2.3433</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7875</v>
+        <v>2.0307</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4836</v>
+        <v>1.568</v>
       </c>
       <c r="U4" t="n">
-        <v>0.304</v>
+        <v>0.4627</v>
       </c>
       <c r="V4" t="n">
         <v>1.8488</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3648</v>
+        <v>3.6823</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4515</v>
+        <v>2.0054</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9134</v>
+        <v>1.6769</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4788</v>
+        <v>3.1757</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1776</v>
+        <v>-0.4171</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6564</v>
+        <v>3.5928</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4965</v>
+        <v>2.8732</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.2215</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5912</v>
+        <v>3.0947</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0177</v>
+        <v>0.3024</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0829</v>
+        <v>-0.1956</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.4981</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3954</v>
+        <v>0.6953</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5401</v>
+        <v>0.0757</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8554</v>
+        <v>0.6196</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8868</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3449</v>
+        <v>3.628</v>
       </c>
       <c r="E6" t="n">
-        <v>2.597</v>
+        <v>2.0124</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7479</v>
+        <v>1.6156</v>
       </c>
       <c r="G6" t="n">
         <v>1.1962</v>
@@ -922,13 +922,13 @@
         <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3185</v>
+        <v>1.6016</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6547</v>
+        <v>1.0701</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6637</v>
+        <v>0.5314</v>
       </c>
       <c r="V6" t="n">
         <v>0.6415999999999999</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4981</v>
+        <v>3.5401</v>
       </c>
       <c r="E7" t="n">
-        <v>3.291</v>
+        <v>3.5446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2071</v>
+        <v>-0.0045</v>
       </c>
       <c r="G7" t="n">
         <v>2.657</v>
@@ -1000,13 +1000,13 @@
         <v>1.3209</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7654</v>
+        <v>0.8074</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1735</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9389</v>
+        <v>0.7272</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2157</v>
+        <v>2.4667</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4594</v>
+        <v>1.3998</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7562</v>
+        <v>1.0668</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1757</v>
+        <v>2.4788</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4171</v>
+        <v>-0.1776</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5928</v>
+        <v>2.6564</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8732</v>
+        <v>2.4965</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2215</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0947</v>
+        <v>2.5912</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3024</v>
+        <v>-0.0177</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1956</v>
+        <v>-0.0829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4981</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2287</v>
+        <v>1.4973</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4703</v>
+        <v>0.4884</v>
       </c>
       <c r="U8" t="n">
-        <v>0.699</v>
+        <v>1.0088</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4573</v>
+        <v>2.2737</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8612</v>
+        <v>3.466</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4039</v>
+        <v>-1.1923</v>
       </c>
       <c r="G9" t="n">
         <v>0.1391</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.8892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2323</v>
+        <v>0.3725</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3051</v>
+        <v>0.5168</v>
       </c>
       <c r="V9" t="n">
         <v>0.3018</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SCOTT</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1275</v>
+        <v>1.3607</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2133</v>
+        <v>0.5054</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0858</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1829</v>
+        <v>0.956</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4406</v>
+        <v>0.8757</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3796</v>
+        <v>1.2276</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0634</v>
+        <v>1.1042</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3162</v>
+        <v>0.1234</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1967</v>
+        <v>-0.2716</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.504</v>
+        <v>-0.2285</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6927</v>
+        <v>-0.0431</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5673</v>
+        <v>-0.0858</v>
       </c>
       <c r="T10" t="n">
-        <v>0.532</v>
+        <v>-0.0806</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0353</v>
+        <v>-0.0053</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W10" t="n">
         <v>0.3018</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>L. SCOTT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8387</v>
+        <v>0.7907</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1156</v>
+        <v>1.8236</v>
       </c>
       <c r="F13" t="n">
-        <v>0.723</v>
+        <v>-1.0329</v>
       </c>
       <c r="G13" t="n">
-        <v>0.956</v>
+        <v>0.1829</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8757</v>
+        <v>-0.4406</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0803</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2276</v>
+        <v>1.3796</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1042</v>
+        <v>0.0634</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1234</v>
+        <v>1.3162</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2716</v>
+        <v>-1.1967</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2285</v>
+        <v>-0.504</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0431</v>
+        <v>-0.6927</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6078</v>
+        <v>0.2304</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4703</v>
+        <v>0.1422</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1375</v>
+        <v>0.0882</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0.3018</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. KEITA DIALLO</t>
+          <t>P. TORRES TOVAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7747</v>
+        <v>-1.2117</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2215</v>
+        <v>-2.7934</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5532</v>
+        <v>1.5818</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.8202</v>
+        <v>-2.3866</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7984</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0217</v>
+        <v>-2.3209</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.7028</v>
+        <v>-2.3047</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3086</v>
+        <v>-0.4383</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3943</v>
+        <v>-1.8664</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1173</v>
+        <v>-0.0819</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4899</v>
+        <v>0.3725</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4544</v>
       </c>
       <c r="P14" t="n">
-        <v>1.887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6489</v>
+        <v>0.6844</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4813</v>
+        <v>0.153</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1676</v>
+        <v>0.5314</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4904</v>
+        <v>0.3018</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. TORRES TOVAR</t>
+          <t>D. KEITA DIALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.3493</v>
+        <v>-1.6643</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.5342</v>
+        <v>-0.4551</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1849</v>
+        <v>-1.2093</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3866</v>
+        <v>-2.8202</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-1.7984</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3209</v>
+        <v>-1.0217</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.3047</v>
+        <v>-1.7028</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4383</v>
+        <v>-1.3086</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8664</v>
+        <v>-0.3943</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0819</v>
+        <v>-1.1173</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3725</v>
+        <v>-0.4899</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4544</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4532</v>
+        <v>1.7593</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5879</v>
+        <v>1.2478</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1346</v>
+        <v>0.5115</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3018</v>
+        <v>-2.4904</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>33.9267</v>
+        <v>34.5146</v>
       </c>
       <c r="E16" t="n">
-        <v>24.5898</v>
+        <v>25.1776</v>
       </c>
       <c r="F16" t="n">
-        <v>9.3368</v>
+        <v>9.336899999999998</v>
       </c>
       <c r="G16" t="n">
         <v>17.786</v>
@@ -1672,7 +1672,7 @@
         <v>8.045200000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>9.740699999999999</v>
+        <v>9.740699999999997</v>
       </c>
       <c r="J16" t="n">
         <v>21.8603</v>
@@ -1690,10 +1690,10 @@
         <v>-3.4277</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6468999999999999</v>
+        <v>-0.6468999999999998</v>
       </c>
       <c r="P16" t="n">
-        <v>4.7175</v>
+        <v>4.717499999999999</v>
       </c>
       <c r="Q16" t="n">
         <v>-8.4915</v>
@@ -1702,13 +1702,13 @@
         <v>13.209</v>
       </c>
       <c r="S16" t="n">
-        <v>12.7446</v>
+        <v>13.3324</v>
       </c>
       <c r="T16" t="n">
-        <v>6.354</v>
+        <v>6.941799999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>6.3905</v>
+        <v>6.390299999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3212</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3142</v>
+        <v>3.536</v>
       </c>
       <c r="E17" t="n">
-        <v>6.4257</v>
+        <v>5.9385</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1115</v>
+        <v>-2.4025</v>
       </c>
       <c r="G17" t="n">
         <v>1.7441</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9394</v>
+        <v>-1.7175</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2881</v>
+        <v>-0.7753</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6512</v>
+        <v>-0.9422</v>
       </c>
       <c r="V17" t="n">
         <v>2.1886</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8797</v>
+        <v>-1.8784</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6541</v>
+        <v>1.9464</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5338</v>
+        <v>-3.8248</v>
       </c>
       <c r="G18" t="n">
         <v>1.2121</v>
@@ -1858,13 +1858,13 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8465</v>
+        <v>-0.8452</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1758</v>
+        <v>-0.8834</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3293</v>
+        <v>0.0383</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9244</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DAMESTOY</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4981</v>
+        <v>-2.2959</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5355</v>
+        <v>-1.0831</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0336</v>
+        <v>-1.2128</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0658</v>
+        <v>-2.2645</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2434</v>
+        <v>-1.2944</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1776</v>
+        <v>-0.9701</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8883</v>
+        <v>-0.455</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1479</v>
+        <v>-0.4805</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7403</v>
+        <v>0.0256</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-1.8095</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3913</v>
+        <v>-0.8139</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5628</v>
+        <v>-0.9956</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2627</v>
+        <v>-1.126</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3527</v>
+        <v>-0.6282</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.91</v>
+        <v>-0.4979</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.547</v>
+        <v>0.3398</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>M. DAMESTOY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7024</v>
+        <v>-2.3923</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.278</v>
+        <v>0.5355</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4245</v>
+        <v>-2.9278</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2645</v>
+        <v>-0.0658</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2944</v>
+        <v>-0.2434</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9701</v>
+        <v>0.1776</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.455</v>
+        <v>0.8883</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4805</v>
+        <v>0.1479</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0256</v>
+        <v>0.7403</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8095</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8139</v>
+        <v>-0.3913</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9956</v>
+        <v>-0.5628</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5325</v>
+        <v>-1.1569</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.823</v>
+        <v>-0.3527</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7095</v>
+        <v>-0.8041</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3398</v>
+        <v>-1.547</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3398</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0635</v>
+        <v>-3.7809</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9325</v>
+        <v>-1.8351</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.131</v>
+        <v>-1.9459</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4568</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9841</v>
+        <v>-0.7015</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8789</v>
+        <v>-0.7815</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1052</v>
+        <v>0.08</v>
       </c>
       <c r="V21" t="n">
         <v>0.9434</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3419</v>
+        <v>-4.5025</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6445</v>
+        <v>-2.2547</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6975</v>
+        <v>-2.2477</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4064</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9545</v>
+        <v>-2.1151</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2345</v>
+        <v>-0.8448</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.72</v>
+        <v>-1.2703</v>
       </c>
       <c r="V22" t="n">
         <v>0.019</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.679</v>
+        <v>-5.5371</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6663</v>
+        <v>-0.4714</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0127</v>
+        <v>-5.0656</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8541</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4666</v>
+        <v>-2.3246</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9994</v>
+        <v>-0.8045</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4672</v>
+        <v>-1.5201</v>
       </c>
       <c r="V23" t="n">
         <v>-1.547</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4963</v>
+        <v>-7.2221</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1717</v>
+        <v>-4.9769</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3246</v>
+        <v>-2.2452</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9427</v>
@@ -2326,13 +2326,13 @@
         <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7042</v>
+        <v>-1.4299</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8818</v>
+        <v>-0.6869</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8224</v>
+        <v>-0.743</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6415999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.579800000000001</v>
+        <v>-9.8536</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2593</v>
+        <v>-7.1362</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3206</v>
+        <v>-2.7174</v>
       </c>
       <c r="G25" t="n">
         <v>-8.751799999999999</v>
@@ -2404,13 +2404,13 @@
         <v>1.5096</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0541</v>
+        <v>-1.3278</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2438</v>
+        <v>-0.6331</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2979</v>
+        <v>-0.6947</v>
       </c>
       <c r="V25" t="n">
         <v>2.4904</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-33.9265</v>
+        <v>-33.9268</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.336999999999998</v>
+        <v>-9.337</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.5898</v>
+        <v>-24.5897</v>
       </c>
       <c r="G26" t="n">
         <v>-17.7859</v>
@@ -2482,13 +2482,13 @@
         <v>8.4915</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.7446</v>
+        <v>-12.7445</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.3904</v>
+        <v>-6.390400000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.3541</v>
+        <v>-6.354</v>
       </c>
       <c r="V26" t="n">
         <v>1.321200000000001</v>
